--- a/TODO/template.xlsx
+++ b/TODO/template.xlsx
@@ -265,21 +265,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -483,7 +475,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AV5"/>
   <sheetFormatPr defaultColWidth="10.5859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="10.58"/>
@@ -507,321 +499,175 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="49" style="1" width="10.58"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="n">
+    <row r="1" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="n">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="n">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="n">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="n">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="n">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="n">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="n">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="2" t="n">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="n">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="2" t="n">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="2" t="n">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="2" t="n">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="2" t="n">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="2" t="n">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="2" t="n">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="2" t="n">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="2" t="n">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="2" t="n">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="2" t="n">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="2" t="n">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="2" t="n">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="2" t="n">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="X1" s="2" t="n">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="2" t="n">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" s="2" t="n">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" s="2" t="n">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" s="2" t="n">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AC1" s="2" t="n">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" s="2" t="n">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AE1" s="2" t="n">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AF1" s="2" t="n">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" s="2" t="n">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AH1" s="2" t="n">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AI1" s="2" t="n">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AJ1" s="2" t="n">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AK1" s="2" t="n">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AL1" s="2" t="n">
+      <c r="AM1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AM1" s="2" t="n">
+      <c r="AN1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AN1" s="2" t="n">
+      <c r="AO1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AO1" s="2" t="n">
+      <c r="AP1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AP1" s="2" t="n">
+      <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AQ1" s="2" t="n">
+      <c r="AR1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AR1" s="2" t="n">
+      <c r="AS1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AS1" s="2" t="n">
+      <c r="AT1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AT1" s="2" t="n">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AU1" s="2" t="n">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AV1" s="2" t="n">
-        <v>48</v>
-      </c>
     </row>
-    <row r="2" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV2" s="4" t="s">
-        <v>47</v>
-      </c>
+    <row r="2" s="4" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
     </row>
-    <row r="3" s="6" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="V3" s="4"/>
-      <c r="AP3" s="4"/>
-      <c r="AQ3" s="4"/>
-      <c r="AR3" s="4"/>
+    <row r="3" s="4" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V3" s="2"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="2"/>
     </row>
-    <row r="4" s="6" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="V4" s="4"/>
-      <c r="AP4" s="4"/>
-      <c r="AQ4" s="4"/>
-      <c r="AR4" s="4"/>
+    <row r="4" s="4" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
     </row>
-    <row r="5" s="6" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="V5" s="4"/>
-      <c r="AP5" s="4"/>
-      <c r="AQ5" s="4"/>
-      <c r="AR5" s="4"/>
-    </row>
-    <row r="6" s="6" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="V6" s="4"/>
-      <c r="AP6" s="4"/>
-      <c r="AQ6" s="4"/>
-      <c r="AR6" s="4"/>
+    <row r="5" s="4" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V5" s="2"/>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2"/>
+      <c r="AR5" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/TODO/template.xlsx
+++ b/TODO/template.xlsx
@@ -25,10 +25,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
-    <t xml:space="preserve">Факультет собственник(аббревиатура)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Факультет исполнитель(аббревиатура)</t>
+    <t xml:space="preserve">Факультет собственник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Факультет исполнитель</t>
   </si>
   <si>
     <t xml:space="preserve">Наименование кафедры исполнителя</t>
